--- a/Modelo_Planilha_Spools.xlsx
+++ b/Modelo_Planilha_Spools.xlsx
@@ -1,41 +1,179 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MORAIS\Documentos\GitHub\avanco-tubulacao\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FFF4C1-64C2-4E2E-8C09-D542EE64C2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="1680" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+  <si>
+    <t>Isométrico</t>
+  </si>
+  <si>
+    <t>Spool</t>
+  </si>
+  <si>
+    <t>Linha</t>
+  </si>
+  <si>
+    <t>Sistema</t>
+  </si>
+  <si>
+    <t>Peso (kg)</t>
+  </si>
+  <si>
+    <t>Status Fabricação</t>
+  </si>
+  <si>
+    <t>Status Montagem</t>
+  </si>
+  <si>
+    <t>Pacote SOP</t>
+  </si>
+  <si>
+    <t>Sistema STH</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Data Liberado Montagem (Fabricado)</t>
+  </si>
+  <si>
+    <t>Data Programação Montagem (Programado)</t>
+  </si>
+  <si>
+    <t>Data Pré Montagem</t>
+  </si>
+  <si>
+    <t>Data Ajuste Campo (Visual Ajuste)</t>
+  </si>
+  <si>
+    <t>Data Solda Campo (Soldado)</t>
+  </si>
+  <si>
+    <t>Data VS Campo (Visual Solda)</t>
+  </si>
+  <si>
+    <t>Data Liberado Campo (Liberado END)</t>
+  </si>
+  <si>
+    <t>Data STH (Teste Hidrostático)</t>
+  </si>
+  <si>
+    <t>16"-HC-4710-05101-C5</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>16"-HC-4710-05101-C5-AC</t>
+  </si>
+  <si>
+    <t>U4710</t>
+  </si>
+  <si>
+    <t>37 - LIBERADO PARA MONTAGEM</t>
+  </si>
+  <si>
+    <t>53 - CONCLUIDO</t>
+  </si>
+  <si>
+    <t>SOP-U-4710-PR-0001</t>
+  </si>
+  <si>
+    <t>STH-4710-01</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>16"-HC-4710-05102-C5</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>16"-HC-4710-05102-C5-AC</t>
+  </si>
+  <si>
+    <t>36 - NAO INICIADA A MONTAGEM</t>
+  </si>
+  <si>
+    <t>4"-AI-4710-04146-C5</t>
+  </si>
+  <si>
+    <t>4"-AI-4710-04146-C5-NI</t>
+  </si>
+  <si>
+    <t>02 - AGUARDANDO MATERIAL</t>
+  </si>
+  <si>
+    <t>SOP-U-4710-UT-1011</t>
+  </si>
+  <si>
+    <t>STH-4710-02</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>10"-HD-4730-05202-C5</t>
+  </si>
+  <si>
+    <t>10"-HD-4730-05202-C5-AL</t>
+  </si>
+  <si>
+    <t>U4730</t>
+  </si>
+  <si>
+    <t>SOP-U-4730-PR-0100</t>
+  </si>
+  <si>
+    <t>STH-4730-01</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>2"-CV-CIVIL-00012-C5</t>
+  </si>
+  <si>
+    <t>2"-CV-CIVIL-00012-C5-AC</t>
+  </si>
+  <si>
+    <t>CIVIL</t>
+  </si>
+  <si>
+    <t>SOP-CIVIL-PR-0001</t>
+  </si>
+  <si>
+    <t>STH-CIVIL-01</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="166" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -43,13 +181,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,15 +216,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,332 +558,346 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="34.83203125" customWidth="1"/>
-    <col min="12" max="12" width="38.83203125" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" customWidth="1"/>
-    <col min="14" max="14" width="33.83203125" customWidth="1"/>
-    <col min="15" max="15" width="26.83203125" customWidth="1"/>
-    <col min="16" max="16" width="28.83203125" customWidth="1"/>
-    <col min="17" max="17" width="34.83203125" customWidth="1"/>
-    <col min="18" max="18" width="29.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="38.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.796875" customWidth="1"/>
+    <col min="14" max="14" width="30" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.09765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.8984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Isométrico</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Spool</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Linha</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Sistema</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Peso (kg)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Status Fabricação</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Status Montagem</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Pacote SOP</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Sistema STH</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Material</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Data Liberado Montagem (Fabricado)</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Data Programação Montagem (Programado)</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Data Pré Montagem</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Data Ajuste Campo (Visual Ajuste)</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Data Solda Campo (Soldado)</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Data VS Campo (Visual Solda)</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Data Liberado Campo (Liberado END)</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Data STH (Teste Hidrostático)</v>
+    <row r="1" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>16"-HC-4710-05101-C5</v>
-      </c>
-      <c r="B2" t="str">
-        <v>A</v>
-      </c>
-      <c r="C2" t="str">
-        <v>16"-HC-4710-05101-C5-AC</v>
-      </c>
-      <c r="D2" t="str">
-        <v>U4710</v>
+    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
       </c>
       <c r="E2">
         <v>4200</v>
       </c>
-      <c r="F2" t="str">
-        <v>37 - LIBERADO PARA MONTAGEM</v>
-      </c>
-      <c r="G2" t="str">
-        <v>53 - CONCLUIDO</v>
-      </c>
-      <c r="H2" t="str">
-        <v>SOP-U-4710-PR-0001</v>
-      </c>
-      <c r="I2" t="str">
-        <v>STH-4710-01</v>
-      </c>
-      <c r="J2" t="str">
-        <v>AC</v>
-      </c>
-      <c r="K2" s="1">
-        <v>45360.99967592592</v>
-      </c>
-      <c r="L2" s="1">
-        <v>45341.99967592592</v>
-      </c>
-      <c r="M2" s="1">
-        <v>45362.99967592592</v>
-      </c>
-      <c r="N2" s="1">
-        <v>45364.99967592592</v>
-      </c>
-      <c r="O2" s="1">
-        <v>45365.99967592592</v>
-      </c>
-      <c r="P2" s="1">
-        <v>45366.99967592592</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>45370.99967592592</v>
-      </c>
-      <c r="R2" s="1">
-        <v>45383.99967592592</v>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="2">
+        <v>45360.999675925923</v>
+      </c>
+      <c r="L2" s="2">
+        <v>45341.999675925923</v>
+      </c>
+      <c r="M2" s="2">
+        <v>45362.999675925923</v>
+      </c>
+      <c r="N2" s="2">
+        <v>45364.999675925923</v>
+      </c>
+      <c r="O2" s="2">
+        <v>45365.999675925923</v>
+      </c>
+      <c r="P2" s="2">
+        <v>45366.999675925923</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>45370.999675925923</v>
+      </c>
+      <c r="R2" s="2">
+        <v>45383.999675925923</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>16"-HC-4710-05102-C5</v>
-      </c>
-      <c r="B3" t="str">
-        <v>B</v>
-      </c>
-      <c r="C3" t="str">
-        <v>16"-HC-4710-05102-C5-AC</v>
-      </c>
-      <c r="D3" t="str">
-        <v>U4710</v>
+    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
       </c>
       <c r="E3">
         <v>3800</v>
       </c>
-      <c r="F3" t="str">
-        <v>37 - LIBERADO PARA MONTAGEM</v>
-      </c>
-      <c r="G3" t="str">
-        <v>36 - NAO INICIADA A MONTAGEM</v>
-      </c>
-      <c r="H3" t="str">
-        <v>SOP-U-4710-PR-0001</v>
-      </c>
-      <c r="I3" t="str">
-        <v>STH-4710-01</v>
-      </c>
-      <c r="J3" t="str">
-        <v>AC</v>
-      </c>
-      <c r="K3" s="1">
-        <v>45361.99967592592</v>
-      </c>
-      <c r="L3" s="1">
-        <v>45342.99967592592</v>
-      </c>
-      <c r="M3" s="1">
-        <v>45363.99967592592</v>
-      </c>
-      <c r="N3" s="1">
-        <v>45365.99967592592</v>
-      </c>
-      <c r="O3" s="1">
-        <v>45368.99967592592</v>
-      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="2">
+        <v>45361.999675925923</v>
+      </c>
+      <c r="L3" s="2">
+        <v>45342.999675925923</v>
+      </c>
+      <c r="M3" s="2">
+        <v>45363.999675925923</v>
+      </c>
+      <c r="N3" s="2">
+        <v>45365.999675925923</v>
+      </c>
+      <c r="O3" s="2">
+        <v>45368.999675925923</v>
+      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>4"-AI-4710-04146-C5</v>
-      </c>
-      <c r="B4" t="str">
-        <v>A</v>
-      </c>
-      <c r="C4" t="str">
-        <v>4"-AI-4710-04146-C5-NI</v>
-      </c>
-      <c r="D4" t="str">
-        <v>U4710</v>
+    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
       </c>
       <c r="E4">
         <v>210.5</v>
       </c>
-      <c r="F4" t="str">
-        <v>02 - AGUARDANDO MATERIAL</v>
-      </c>
-      <c r="G4" t="str">
-        <v>36 - NAO INICIADA A MONTAGEM</v>
-      </c>
-      <c r="H4" t="str">
-        <v>SOP-U-4710-UT-1011</v>
-      </c>
-      <c r="I4" t="str">
-        <v>STH-4710-02</v>
-      </c>
-      <c r="J4" t="str">
-        <v>AI</v>
-      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>10"-HD-4730-05202-C5</v>
-      </c>
-      <c r="B5" t="str">
-        <v>A</v>
-      </c>
-      <c r="C5" t="str">
-        <v>10"-HD-4730-05202-C5-AL</v>
-      </c>
-      <c r="D5" t="str">
-        <v>U4730</v>
+    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
       </c>
       <c r="E5">
         <v>774.3</v>
       </c>
-      <c r="F5" t="str">
-        <v>37 - LIBERADO PARA MONTAGEM</v>
-      </c>
-      <c r="G5" t="str">
-        <v>37 - LIBERADO PARA MONTAGEM</v>
-      </c>
-      <c r="H5" t="str">
-        <v>SOP-U-4730-PR-0100</v>
-      </c>
-      <c r="I5" t="str">
-        <v>STH-4730-01</v>
-      </c>
-      <c r="J5" t="str">
-        <v>AL</v>
-      </c>
-      <c r="K5" s="1">
-        <v>45386.99967592592</v>
-      </c>
-      <c r="L5" s="1">
-        <v>45370.99967592592</v>
-      </c>
-      <c r="M5" s="1">
-        <v>45388.99967592592</v>
-      </c>
-      <c r="N5" s="1">
-        <v>45390.99967592592</v>
-      </c>
-      <c r="O5" s="1">
-        <v>45391.99967592592</v>
-      </c>
-      <c r="P5" s="1">
-        <v>45392.99967592592</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>45399.99967592592</v>
-      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="2">
+        <v>45386.999675925923</v>
+      </c>
+      <c r="L5" s="2">
+        <v>45370.999675925923</v>
+      </c>
+      <c r="M5" s="2">
+        <v>45388.999675925923</v>
+      </c>
+      <c r="N5" s="2">
+        <v>45390.999675925923</v>
+      </c>
+      <c r="O5" s="2">
+        <v>45391.999675925923</v>
+      </c>
+      <c r="P5" s="2">
+        <v>45392.999675925923</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>45399.999675925923</v>
+      </c>
+      <c r="R5" s="2"/>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2"-CV-CIVIL-00012-C5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>A</v>
-      </c>
-      <c r="C6" t="str">
-        <v>2"-CV-CIVIL-00012-C5-AC</v>
-      </c>
-      <c r="D6" t="str">
-        <v>CIVIL</v>
+    <row r="6" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
       </c>
       <c r="E6">
         <v>18.2</v>
       </c>
-      <c r="F6" t="str">
-        <v>37 - LIBERADO PARA MONTAGEM</v>
-      </c>
-      <c r="G6" t="str">
-        <v>53 - CONCLUIDO</v>
-      </c>
-      <c r="H6" t="str">
-        <v>SOP-CIVIL-PR-0001</v>
-      </c>
-      <c r="I6" t="str">
-        <v>STH-CIVIL-01</v>
-      </c>
-      <c r="J6" t="str">
-        <v>AC</v>
-      </c>
-      <c r="K6" s="1">
-        <v>45305.99967592592</v>
-      </c>
-      <c r="L6" s="1">
-        <v>45295.99967592592</v>
-      </c>
-      <c r="M6" s="1">
-        <v>45307.99967592592</v>
-      </c>
-      <c r="N6" s="1">
-        <v>45308.99967592592</v>
-      </c>
-      <c r="O6" s="1">
-        <v>45309.99967592592</v>
-      </c>
-      <c r="P6" s="1">
-        <v>45309.99967592592</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>45315.99967592592</v>
-      </c>
-      <c r="R6" s="1">
-        <v>45324.99967592592</v>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="2">
+        <v>45305.999675925923</v>
+      </c>
+      <c r="L6" s="2">
+        <v>45295.999675925923</v>
+      </c>
+      <c r="M6" s="2">
+        <v>45307.999675925923</v>
+      </c>
+      <c r="N6" s="2">
+        <v>45308.999675925923</v>
+      </c>
+      <c r="O6" s="2">
+        <v>45309.999675925923</v>
+      </c>
+      <c r="P6" s="2">
+        <v>45309.999675925923</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>45315.999675925923</v>
+      </c>
+      <c r="R6" s="2">
+        <v>45324.999675925923</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R6"/>
+    <ignoredError sqref="A1:R6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>